--- a/Template.xlsx
+++ b/Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Charlie NextCloud\Spyro\Documents\Projects\Cardmarket-Price-Updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE693DB3-D677-43D2-97C9-5165C62ED8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000B23DD-0E08-43E1-A51E-978F9737327D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Red-Eyes Black Dragon Collectio" sheetId="1" r:id="rId1"/>
     <sheet name="Formatting" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>Release Date</t>
   </si>
@@ -146,12 +146,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\£#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="£#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,7 +260,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5999938962981048"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -290,65 +289,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="5" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="6" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF92D050"/>
@@ -408,166 +404,6 @@
       <font>
         <color rgb="FF00B050"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff00b050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ffff0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ffc00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="ffff0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.3999450666829432"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff92d050"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="ff00b050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff00b050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ffff0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ffc00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="ffff0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.3999450666829432"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff92d050"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="ff00b050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff00b050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ffff0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ffc00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="ffff0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.3999450666829432"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff92d050"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="ff00b050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff00b050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ffff0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ffc00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="ffff0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.3999450666829432"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff92d050"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="ff00b050"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -887,21 +723,21 @@
   <dimension ref="A1:M59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="31.5703125" customWidth="1" style="6"/>
-    <col min="4" max="4" bestFit="1" width="15" customWidth="1" style="8"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1" style="7"/>
-    <col min="6" max="6" bestFit="1" width="13.7109375" customWidth="1" style="5"/>
-    <col min="7" max="7" bestFit="1" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="32.7109375" customWidth="1" style="6"/>
-    <col min="9" max="9" bestFit="1" width="10.28515625" customWidth="1" style="1"/>
-    <col min="10" max="10" bestFit="1" width="13.5703125" customWidth="1" style="7"/>
-    <col min="11" max="11" bestFit="1" width="32.5703125" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -936,7 +772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>45912</v>
       </c>
@@ -949,7 +785,7 @@
       <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="10">
         <v>552.5</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -969,10 +805,10 @@
       </c>
       <c r="K2" s="11">
         <f>SUMIFS(E:E, I:I, "&lt;&gt;✖", I:I, "&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>28934.37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>37323</v>
       </c>
@@ -985,8 +821,8 @@
       <c r="D3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="20">
-        <v>74.49</v>
+      <c r="E3" s="10">
+        <v>74.489999999999995</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>14</v>
@@ -1007,7 +843,7 @@
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>34186</v>
       </c>
@@ -1018,7 +854,7 @@
         <v>23</v>
       </c>
       <c r="D4" s="9"/>
-      <c r="E4" s="20">
+      <c r="E4" s="10">
         <v>26328.87</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1043,7 +879,7 @@
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>36169</v>
       </c>
@@ -1054,7 +890,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="20">
+      <c r="E5" s="10">
         <v>2053</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1078,7 +914,7 @@
       <c r="L5" s="14"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="1"/>
@@ -1090,12 +926,12 @@
       <c r="J6" s="11"/>
       <c r="K6" s="12">
         <f>SUM(E:E)-K2</f>
-        <v>0</v>
+        <v>74.490000000001601</v>
       </c>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="1"/>
@@ -1109,7 +945,7 @@
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="1"/>
@@ -1123,7 +959,7 @@
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="1"/>
@@ -1137,7 +973,7 @@
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
       <c r="C10" s="1"/>
@@ -1151,7 +987,7 @@
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="1"/>
@@ -1165,7 +1001,7 @@
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="1"/>
@@ -1179,7 +1015,7 @@
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="1"/>
@@ -1193,7 +1029,7 @@
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="1"/>
@@ -1207,7 +1043,7 @@
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="1"/>
@@ -1221,7 +1057,7 @@
       <c r="L15" s="14"/>
       <c r="M15" s="14"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="1"/>
@@ -1235,7 +1071,7 @@
       <c r="L16" s="14"/>
       <c r="M16" s="14"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="1"/>
@@ -1249,7 +1085,7 @@
       <c r="L17" s="14"/>
       <c r="M17" s="14"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="1"/>
@@ -1263,7 +1099,7 @@
       <c r="L18" s="14"/>
       <c r="M18" s="14"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="1"/>
@@ -1277,7 +1113,7 @@
       <c r="L19" s="14"/>
       <c r="M19" s="14"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="1"/>
@@ -1291,7 +1127,7 @@
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="1"/>
@@ -1305,7 +1141,7 @@
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="1"/>
@@ -1319,7 +1155,7 @@
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="1"/>
@@ -1333,7 +1169,7 @@
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="1"/>
@@ -1347,7 +1183,7 @@
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="1"/>
@@ -1361,7 +1197,7 @@
       <c r="L25" s="14"/>
       <c r="M25" s="14"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="1"/>
@@ -1375,7 +1211,7 @@
       <c r="L26" s="14"/>
       <c r="M26" s="14"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="1"/>
@@ -1389,7 +1225,7 @@
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="1"/>
@@ -1403,7 +1239,7 @@
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="1"/>
@@ -1417,7 +1253,7 @@
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="1"/>
@@ -1431,7 +1267,7 @@
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="1"/>
@@ -1445,7 +1281,7 @@
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="1"/>
@@ -1459,7 +1295,7 @@
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="1"/>
@@ -1473,7 +1309,7 @@
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="1"/>
@@ -1487,7 +1323,7 @@
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="1"/>
@@ -1501,7 +1337,7 @@
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="13"/>
       <c r="C36" s="1"/>
@@ -1515,7 +1351,7 @@
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="1"/>
@@ -1529,7 +1365,7 @@
       <c r="L37" s="14"/>
       <c r="M37" s="14"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
       <c r="C38" s="1"/>
@@ -1543,7 +1379,7 @@
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="1"/>
@@ -1557,7 +1393,7 @@
       <c r="L39" s="14"/>
       <c r="M39" s="14"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="13"/>
       <c r="C40" s="1"/>
@@ -1571,7 +1407,7 @@
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="1"/>
@@ -1585,7 +1421,7 @@
       <c r="L41" s="14"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="13"/>
       <c r="C42" s="1"/>
@@ -1599,7 +1435,7 @@
       <c r="L42" s="14"/>
       <c r="M42" s="14"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="1"/>
@@ -1613,7 +1449,7 @@
       <c r="L43" s="14"/>
       <c r="M43" s="14"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="1"/>
@@ -1627,7 +1463,7 @@
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="1"/>
@@ -1641,7 +1477,7 @@
       <c r="L45" s="14"/>
       <c r="M45" s="14"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="1"/>
@@ -1655,7 +1491,7 @@
       <c r="L46" s="14"/>
       <c r="M46" s="14"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="1"/>
@@ -1669,7 +1505,7 @@
       <c r="L47" s="14"/>
       <c r="M47" s="14"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="1"/>
@@ -1683,7 +1519,7 @@
       <c r="L48" s="14"/>
       <c r="M48" s="14"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="1"/>
@@ -1697,7 +1533,7 @@
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="1"/>
@@ -1711,7 +1547,7 @@
       <c r="L50" s="14"/>
       <c r="M50" s="14"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="1"/>
@@ -1725,7 +1561,7 @@
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
       <c r="B52" s="13"/>
       <c r="C52" s="1"/>
@@ -1739,7 +1575,7 @@
       <c r="L52" s="14"/>
       <c r="M52" s="14"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="13"/>
       <c r="B53" s="13"/>
       <c r="C53" s="1"/>
@@ -1753,7 +1589,7 @@
       <c r="L53" s="14"/>
       <c r="M53" s="14"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
       <c r="C54" s="1"/>
@@ -1767,7 +1603,7 @@
       <c r="L54" s="14"/>
       <c r="M54" s="14"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="13"/>
       <c r="B55" s="13"/>
       <c r="C55" s="1"/>
@@ -1781,7 +1617,7 @@
       <c r="L55" s="14"/>
       <c r="M55" s="14"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="13"/>
       <c r="B56" s="13"/>
       <c r="C56" s="1"/>
@@ -1795,7 +1631,7 @@
       <c r="L56" s="14"/>
       <c r="M56" s="14"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
       <c r="B57" s="13"/>
       <c r="C57" s="1"/>
@@ -1809,7 +1645,7 @@
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="13"/>
       <c r="B58" s="13"/>
       <c r="C58" s="1"/>
@@ -1823,7 +1659,7 @@
       <c r="L58" s="14"/>
       <c r="M58" s="14"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="13"/>
       <c r="B59" s="13"/>
       <c r="C59" s="1"/>
@@ -1839,29 +1675,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E59">
-    <cfRule type="aboveAverage" dxfId="22" priority="1" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="23" priority="2"/>
+    <cfRule type="aboveAverage" dxfId="6" priority="1" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I1048576">
-    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="✖">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="✖">
       <formula>NOT(ISERROR(SEARCH("✖",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="6" operator="containsText" text="Unlimited">
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Unlimited">
       <formula>NOT(ISERROR(SEARCH("Unlimited",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="LIMITED">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="LIMITED">
       <formula>NOT(ISERROR(SEARCH("LIMITED",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="8" operator="containsText" text="✔">
+    <cfRule type="containsText" dxfId="1" priority="8" operator="containsText" text="✔">
       <formula>NOT(ISERROR(SEARCH("✔",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="1st Edition">
+    <cfRule type="containsText" dxfId="0" priority="9" operator="containsText" text="1st Edition">
       <formula>NOT(ISERROR(SEARCH("1st Edition",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
-  <headerFooter/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -1888,11 +1723,11 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" bestFit="1" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
@@ -1903,7 +1738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
@@ -1911,7 +1746,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -1919,38 +1754,32 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ProfessorShroom under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Template.xlsx
+++ b/Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Charlie NextCloud\Spyro\Documents\Projects\Software\Cardmarket-Price-Updater\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Nextcloud\Spyro\Documents\Projects\Software\Cardmarket-Price-Updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F758BE-177E-4BF7-8AB2-6D112E141B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42CBE37-F2A5-4483-8E3F-CDDE8200FB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,6 +26,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -273,9 +276,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -305,6 +305,9 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,9 +458,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -495,7 +498,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -601,7 +604,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -743,7 +746,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -754,57 +757,57 @@
   <dimension ref="A1:O673"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
@@ -818,89 +821,89 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="15">
         <v>45912</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>237.33</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <v>845882</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="13" t="str">
+      <c r="J2" s="12" t="str">
         <f>IF(K2="","",IF(K2="✖","✖","✔"))</f>
         <v>✔</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="13">
         <v>200</v>
       </c>
       <c r="M2" s="2">
         <f>SUMIFS(F:F, J:J, "&lt;&gt;✖", J:J, "&lt;&gt;")</f>
         <v>28082.23</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="6">
         <f>COUNTIF(K:K,"✖")</f>
         <v>1</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="7">
         <f>COUNTIFS(K$2:K$1048576,"&lt;&gt;✖",K$2:K$1048576,"&lt;&gt;")</f>
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <v>37323</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>158.11000000000001</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>577919</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="13" t="str">
+      <c r="J3" s="12" t="str">
         <f t="shared" ref="J3:J66" si="0">IF(K3="","",IF(K3="✖","✖","✔"))</f>
         <v>✖</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="5" t="s">
@@ -910,38 +913,38 @@
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <v>34186</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>26328.87</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>5465</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="13" t="str">
+      <c r="J4" s="12" t="str">
         <f t="shared" si="0"/>
         <v>✔</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="13">
         <v>20000</v>
       </c>
       <c r="M4" s="2">
@@ -952,41 +955,41 @@
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>36169</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>1248.46</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <v>660224</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="13" t="str">
+      <c r="J5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>✔</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>2000</v>
       </c>
       <c r="M5" s="5" t="s">
@@ -996,38 +999,38 @@
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="16">
         <v>39770</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>267.57</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>108490</v>
       </c>
-      <c r="J6" s="13" t="str">
+      <c r="J6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>✔</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="13">
         <v>50</v>
       </c>
       <c r="M6" s="3">
@@ -1038,8 +1041,8 @@
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F7" s="11"/>
-      <c r="J7" s="13" t="str">
+      <c r="F7" s="10"/>
+      <c r="J7" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1048,8 +1051,8 @@
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F8" s="11"/>
-      <c r="J8" s="13" t="str">
+      <c r="F8" s="10"/>
+      <c r="J8" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1058,8 +1061,8 @@
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F9" s="11"/>
-      <c r="J9" s="13" t="str">
+      <c r="F9" s="10"/>
+      <c r="J9" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1068,8 +1071,8 @@
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F10" s="11"/>
-      <c r="J10" s="13" t="str">
+      <c r="F10" s="10"/>
+      <c r="J10" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1078,8 +1081,8 @@
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F11" s="11"/>
-      <c r="J11" s="13" t="str">
+      <c r="F11" s="10"/>
+      <c r="J11" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1088,8 +1091,8 @@
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F12" s="11"/>
-      <c r="J12" s="13" t="str">
+      <c r="F12" s="10"/>
+      <c r="J12" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1098,8 +1101,8 @@
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F13" s="11"/>
-      <c r="J13" s="13" t="str">
+      <c r="F13" s="10"/>
+      <c r="J13" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1108,8 +1111,8 @@
       <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F14" s="11"/>
-      <c r="J14" s="13" t="str">
+      <c r="F14" s="10"/>
+      <c r="J14" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1118,8 +1121,8 @@
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F15" s="11"/>
-      <c r="J15" s="13" t="str">
+      <c r="F15" s="10"/>
+      <c r="J15" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1128,8 +1131,8 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F16" s="11"/>
-      <c r="J16" s="13" t="str">
+      <c r="F16" s="10"/>
+      <c r="J16" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1138,8 +1141,8 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F17" s="11"/>
-      <c r="J17" s="13" t="str">
+      <c r="F17" s="10"/>
+      <c r="J17" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1148,8 +1151,8 @@
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F18" s="11"/>
-      <c r="J18" s="13" t="str">
+      <c r="F18" s="10"/>
+      <c r="J18" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1158,8 +1161,8 @@
       <c r="O18" s="4"/>
     </row>
     <row r="19" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F19" s="11"/>
-      <c r="J19" s="13" t="str">
+      <c r="F19" s="10"/>
+      <c r="J19" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1168,8 +1171,8 @@
       <c r="O19" s="4"/>
     </row>
     <row r="20" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F20" s="11"/>
-      <c r="J20" s="13" t="str">
+      <c r="F20" s="10"/>
+      <c r="J20" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1178,8 +1181,8 @@
       <c r="O20" s="4"/>
     </row>
     <row r="21" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F21" s="11"/>
-      <c r="J21" s="13" t="str">
+      <c r="F21" s="10"/>
+      <c r="J21" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1188,8 +1191,8 @@
       <c r="O21" s="4"/>
     </row>
     <row r="22" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F22" s="11"/>
-      <c r="J22" s="13" t="str">
+      <c r="F22" s="10"/>
+      <c r="J22" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1198,8 +1201,8 @@
       <c r="O22" s="4"/>
     </row>
     <row r="23" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F23" s="11"/>
-      <c r="J23" s="13" t="str">
+      <c r="F23" s="10"/>
+      <c r="J23" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1208,8 +1211,8 @@
       <c r="O23" s="4"/>
     </row>
     <row r="24" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F24" s="11"/>
-      <c r="J24" s="13" t="str">
+      <c r="F24" s="10"/>
+      <c r="J24" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1218,8 +1221,8 @@
       <c r="O24" s="4"/>
     </row>
     <row r="25" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F25" s="11"/>
-      <c r="J25" s="13" t="str">
+      <c r="F25" s="10"/>
+      <c r="J25" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1228,8 +1231,8 @@
       <c r="O25" s="4"/>
     </row>
     <row r="26" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F26" s="11"/>
-      <c r="J26" s="13" t="str">
+      <c r="F26" s="10"/>
+      <c r="J26" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1238,8 +1241,8 @@
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F27" s="11"/>
-      <c r="J27" s="13" t="str">
+      <c r="F27" s="10"/>
+      <c r="J27" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1248,8 +1251,8 @@
       <c r="O27" s="4"/>
     </row>
     <row r="28" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F28" s="11"/>
-      <c r="J28" s="13" t="str">
+      <c r="F28" s="10"/>
+      <c r="J28" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1258,8 +1261,8 @@
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F29" s="11"/>
-      <c r="J29" s="13" t="str">
+      <c r="F29" s="10"/>
+      <c r="J29" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1268,8 +1271,8 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F30" s="11"/>
-      <c r="J30" s="13" t="str">
+      <c r="F30" s="10"/>
+      <c r="J30" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1278,8 +1281,8 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F31" s="11"/>
-      <c r="J31" s="13" t="str">
+      <c r="F31" s="10"/>
+      <c r="J31" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1288,8 +1291,8 @@
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F32" s="11"/>
-      <c r="J32" s="13" t="str">
+      <c r="F32" s="10"/>
+      <c r="J32" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1298,8 +1301,8 @@
       <c r="O32" s="4"/>
     </row>
     <row r="33" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F33" s="11"/>
-      <c r="J33" s="13" t="str">
+      <c r="F33" s="10"/>
+      <c r="J33" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1308,8 +1311,8 @@
       <c r="O33" s="4"/>
     </row>
     <row r="34" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F34" s="11"/>
-      <c r="J34" s="13" t="str">
+      <c r="F34" s="10"/>
+      <c r="J34" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1318,8 +1321,8 @@
       <c r="O34" s="4"/>
     </row>
     <row r="35" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F35" s="11"/>
-      <c r="J35" s="13" t="str">
+      <c r="F35" s="10"/>
+      <c r="J35" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1328,8 +1331,8 @@
       <c r="O35" s="4"/>
     </row>
     <row r="36" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F36" s="11"/>
-      <c r="J36" s="13" t="str">
+      <c r="F36" s="10"/>
+      <c r="J36" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1338,8 +1341,8 @@
       <c r="O36" s="4"/>
     </row>
     <row r="37" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F37" s="11"/>
-      <c r="J37" s="13" t="str">
+      <c r="F37" s="10"/>
+      <c r="J37" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1348,8 +1351,8 @@
       <c r="O37" s="4"/>
     </row>
     <row r="38" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F38" s="11"/>
-      <c r="J38" s="13" t="str">
+      <c r="F38" s="10"/>
+      <c r="J38" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1358,8 +1361,8 @@
       <c r="O38" s="4"/>
     </row>
     <row r="39" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F39" s="11"/>
-      <c r="J39" s="13" t="str">
+      <c r="F39" s="10"/>
+      <c r="J39" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1368,8 +1371,8 @@
       <c r="O39" s="4"/>
     </row>
     <row r="40" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F40" s="11"/>
-      <c r="J40" s="13" t="str">
+      <c r="F40" s="10"/>
+      <c r="J40" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1378,8 +1381,8 @@
       <c r="O40" s="4"/>
     </row>
     <row r="41" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F41" s="11"/>
-      <c r="J41" s="13" t="str">
+      <c r="F41" s="10"/>
+      <c r="J41" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1388,8 +1391,8 @@
       <c r="O41" s="4"/>
     </row>
     <row r="42" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F42" s="11"/>
-      <c r="J42" s="13" t="str">
+      <c r="F42" s="10"/>
+      <c r="J42" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1398,8 +1401,8 @@
       <c r="O42" s="4"/>
     </row>
     <row r="43" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F43" s="11"/>
-      <c r="J43" s="13" t="str">
+      <c r="F43" s="10"/>
+      <c r="J43" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1408,8 +1411,8 @@
       <c r="O43" s="4"/>
     </row>
     <row r="44" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F44" s="11"/>
-      <c r="J44" s="13" t="str">
+      <c r="F44" s="10"/>
+      <c r="J44" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1418,8 +1421,8 @@
       <c r="O44" s="4"/>
     </row>
     <row r="45" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F45" s="11"/>
-      <c r="J45" s="13" t="str">
+      <c r="F45" s="10"/>
+      <c r="J45" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1428,8 +1431,8 @@
       <c r="O45" s="4"/>
     </row>
     <row r="46" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F46" s="11"/>
-      <c r="J46" s="13" t="str">
+      <c r="F46" s="10"/>
+      <c r="J46" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1438,8 +1441,8 @@
       <c r="O46" s="4"/>
     </row>
     <row r="47" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F47" s="11"/>
-      <c r="J47" s="13" t="str">
+      <c r="F47" s="10"/>
+      <c r="J47" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1448,8 +1451,8 @@
       <c r="O47" s="4"/>
     </row>
     <row r="48" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F48" s="11"/>
-      <c r="J48" s="13" t="str">
+      <c r="F48" s="10"/>
+      <c r="J48" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1458,8 +1461,8 @@
       <c r="O48" s="4"/>
     </row>
     <row r="49" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F49" s="11"/>
-      <c r="J49" s="13" t="str">
+      <c r="F49" s="10"/>
+      <c r="J49" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1468,8 +1471,8 @@
       <c r="O49" s="4"/>
     </row>
     <row r="50" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F50" s="11"/>
-      <c r="J50" s="13" t="str">
+      <c r="F50" s="10"/>
+      <c r="J50" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1478,8 +1481,8 @@
       <c r="O50" s="4"/>
     </row>
     <row r="51" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F51" s="11"/>
-      <c r="J51" s="13" t="str">
+      <c r="F51" s="10"/>
+      <c r="J51" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1488,8 +1491,8 @@
       <c r="O51" s="4"/>
     </row>
     <row r="52" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F52" s="11"/>
-      <c r="J52" s="13" t="str">
+      <c r="F52" s="10"/>
+      <c r="J52" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1498,8 +1501,8 @@
       <c r="O52" s="4"/>
     </row>
     <row r="53" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F53" s="11"/>
-      <c r="J53" s="13" t="str">
+      <c r="F53" s="10"/>
+      <c r="J53" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1508,8 +1511,8 @@
       <c r="O53" s="4"/>
     </row>
     <row r="54" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F54" s="11"/>
-      <c r="J54" s="13" t="str">
+      <c r="F54" s="10"/>
+      <c r="J54" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1518,8 +1521,8 @@
       <c r="O54" s="4"/>
     </row>
     <row r="55" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F55" s="11"/>
-      <c r="J55" s="13" t="str">
+      <c r="F55" s="10"/>
+      <c r="J55" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1528,8 +1531,8 @@
       <c r="O55" s="4"/>
     </row>
     <row r="56" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F56" s="11"/>
-      <c r="J56" s="13" t="str">
+      <c r="F56" s="10"/>
+      <c r="J56" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1538,8 +1541,8 @@
       <c r="O56" s="4"/>
     </row>
     <row r="57" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F57" s="11"/>
-      <c r="J57" s="13" t="str">
+      <c r="F57" s="10"/>
+      <c r="J57" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1548,3701 +1551,3701 @@
       <c r="O57" s="4"/>
     </row>
     <row r="58" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F58" s="11"/>
-      <c r="J58" s="13" t="str">
+      <c r="F58" s="10"/>
+      <c r="J58" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="59" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F59" s="11"/>
-      <c r="J59" s="13" t="str">
+      <c r="F59" s="10"/>
+      <c r="J59" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="60" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F60" s="11"/>
-      <c r="J60" s="13" t="str">
+      <c r="F60" s="10"/>
+      <c r="J60" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="61" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F61" s="11"/>
-      <c r="J61" s="13" t="str">
+      <c r="F61" s="10"/>
+      <c r="J61" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="62" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="J62" s="13" t="str">
+      <c r="J62" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="63" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="J63" s="13" t="str">
+      <c r="J63" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="J64" s="13" t="str">
+      <c r="J64" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="65" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J65" s="13" t="str">
+      <c r="J65" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J66" s="13" t="str">
+      <c r="J66" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J67" s="13" t="str">
+      <c r="J67" s="12" t="str">
         <f t="shared" ref="J67:J130" si="1">IF(K67="","",IF(K67="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="68" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J68" s="13" t="str">
+      <c r="J68" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="69" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J69" s="13" t="str">
+      <c r="J69" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J70" s="13" t="str">
+      <c r="J70" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="71" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J71" s="13" t="str">
+      <c r="J71" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="72" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J72" s="13" t="str">
+      <c r="J72" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="73" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J73" s="13" t="str">
+      <c r="J73" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="74" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J74" s="13" t="str">
+      <c r="J74" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J75" s="13" t="str">
+      <c r="J75" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="76" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J76" s="13" t="str">
+      <c r="J76" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J77" s="13" t="str">
+      <c r="J77" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J78" s="13" t="str">
+      <c r="J78" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J79" s="13" t="str">
+      <c r="J79" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J80" s="13" t="str">
+      <c r="J80" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J81" s="13" t="str">
+      <c r="J81" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J82" s="13" t="str">
+      <c r="J82" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J83" s="13" t="str">
+      <c r="J83" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J84" s="13" t="str">
+      <c r="J84" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="85" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J85" s="13" t="str">
+      <c r="J85" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="86" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J86" s="13" t="str">
+      <c r="J86" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="87" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J87" s="13" t="str">
+      <c r="J87" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="88" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J88" s="13" t="str">
+      <c r="J88" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="89" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J89" s="13" t="str">
+      <c r="J89" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="90" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J90" s="13" t="str">
+      <c r="J90" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="91" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J91" s="13" t="str">
+      <c r="J91" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="92" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J92" s="13" t="str">
+      <c r="J92" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="93" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J93" s="13" t="str">
+      <c r="J93" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="94" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J94" s="13" t="str">
+      <c r="J94" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="95" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J95" s="13" t="str">
+      <c r="J95" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="96" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J96" s="13" t="str">
+      <c r="J96" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="97" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J97" s="13" t="str">
+      <c r="J97" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="98" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J98" s="13" t="str">
+      <c r="J98" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="99" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J99" s="13" t="str">
+      <c r="J99" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="100" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J100" s="13" t="str">
+      <c r="J100" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="101" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J101" s="13" t="str">
+      <c r="J101" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="102" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J102" s="13" t="str">
+      <c r="J102" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="103" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J103" s="13" t="str">
+      <c r="J103" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="104" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J104" s="13" t="str">
+      <c r="J104" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="105" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J105" s="13" t="str">
+      <c r="J105" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="106" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J106" s="13" t="str">
+      <c r="J106" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="107" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J107" s="13" t="str">
+      <c r="J107" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="108" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J108" s="13" t="str">
+      <c r="J108" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="109" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J109" s="13" t="str">
+      <c r="J109" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J110" s="13" t="str">
+      <c r="J110" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="111" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J111" s="13" t="str">
+      <c r="J111" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="112" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J112" s="13" t="str">
+      <c r="J112" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="113" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J113" s="13" t="str">
+      <c r="J113" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="114" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J114" s="13" t="str">
+      <c r="J114" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="115" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J115" s="13" t="str">
+      <c r="J115" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="116" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J116" s="13" t="str">
+      <c r="J116" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="117" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J117" s="13" t="str">
+      <c r="J117" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="118" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J118" s="13" t="str">
+      <c r="J118" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="119" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J119" s="13" t="str">
+      <c r="J119" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="120" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J120" s="13" t="str">
+      <c r="J120" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="121" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J121" s="13" t="str">
+      <c r="J121" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="122" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J122" s="13" t="str">
+      <c r="J122" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="123" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J123" s="13" t="str">
+      <c r="J123" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="124" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J124" s="13" t="str">
+      <c r="J124" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="125" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J125" s="13" t="str">
+      <c r="J125" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="126" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J126" s="13" t="str">
+      <c r="J126" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="127" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J127" s="13" t="str">
+      <c r="J127" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="128" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J128" s="13" t="str">
+      <c r="J128" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="129" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J129" s="13" t="str">
+      <c r="J129" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="130" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J130" s="13" t="str">
+      <c r="J130" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="131" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J131" s="13" t="str">
+      <c r="J131" s="12" t="str">
         <f t="shared" ref="J131:J194" si="2">IF(K131="","",IF(K131="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="132" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J132" s="13" t="str">
+      <c r="J132" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="133" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J133" s="13" t="str">
+      <c r="J133" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="134" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J134" s="13" t="str">
+      <c r="J134" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="135" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J135" s="13" t="str">
+      <c r="J135" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="136" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J136" s="13" t="str">
+      <c r="J136" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="137" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J137" s="13" t="str">
+      <c r="J137" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="138" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J138" s="13" t="str">
+      <c r="J138" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="139" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J139" s="13" t="str">
+      <c r="J139" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="140" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J140" s="13" t="str">
+      <c r="J140" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="141" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J141" s="13" t="str">
+      <c r="J141" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="142" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J142" s="13" t="str">
+      <c r="J142" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="143" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J143" s="13" t="str">
+      <c r="J143" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="144" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J144" s="13" t="str">
+      <c r="J144" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="145" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J145" s="13" t="str">
+      <c r="J145" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="146" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J146" s="13" t="str">
+      <c r="J146" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="147" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J147" s="13" t="str">
+      <c r="J147" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="148" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J148" s="13" t="str">
+      <c r="J148" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="149" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J149" s="13" t="str">
+      <c r="J149" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="150" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J150" s="13" t="str">
+      <c r="J150" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="151" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J151" s="13" t="str">
+      <c r="J151" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="152" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J152" s="13" t="str">
+      <c r="J152" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="153" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J153" s="13" t="str">
+      <c r="J153" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="154" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J154" s="13" t="str">
+      <c r="J154" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="155" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J155" s="13" t="str">
+      <c r="J155" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="156" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J156" s="13" t="str">
+      <c r="J156" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="157" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J157" s="13" t="str">
+      <c r="J157" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="158" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J158" s="13" t="str">
+      <c r="J158" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="159" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J159" s="13" t="str">
+      <c r="J159" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="160" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J160" s="13" t="str">
+      <c r="J160" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="161" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J161" s="13" t="str">
+      <c r="J161" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="162" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J162" s="13" t="str">
+      <c r="J162" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="163" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J163" s="13" t="str">
+      <c r="J163" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="164" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J164" s="13" t="str">
+      <c r="J164" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="165" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J165" s="13" t="str">
+      <c r="J165" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="166" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J166" s="13" t="str">
+      <c r="J166" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="167" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J167" s="13" t="str">
+      <c r="J167" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="168" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J168" s="13" t="str">
+      <c r="J168" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="169" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J169" s="13" t="str">
+      <c r="J169" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="170" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J170" s="13" t="str">
+      <c r="J170" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="171" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J171" s="13" t="str">
+      <c r="J171" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="172" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J172" s="13" t="str">
+      <c r="J172" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="173" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J173" s="13" t="str">
+      <c r="J173" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="174" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J174" s="13" t="str">
+      <c r="J174" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="175" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J175" s="13" t="str">
+      <c r="J175" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="176" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J176" s="13" t="str">
+      <c r="J176" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="177" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J177" s="13" t="str">
+      <c r="J177" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="178" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J178" s="13" t="str">
+      <c r="J178" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="179" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J179" s="13" t="str">
+      <c r="J179" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="180" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J180" s="13" t="str">
+      <c r="J180" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="181" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J181" s="13" t="str">
+      <c r="J181" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="182" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J182" s="13" t="str">
+      <c r="J182" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="183" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J183" s="13" t="str">
+      <c r="J183" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="184" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J184" s="13" t="str">
+      <c r="J184" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="185" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J185" s="13" t="str">
+      <c r="J185" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="186" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J186" s="13" t="str">
+      <c r="J186" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="187" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J187" s="13" t="str">
+      <c r="J187" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="188" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J188" s="13" t="str">
+      <c r="J188" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="189" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J189" s="13" t="str">
+      <c r="J189" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="190" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J190" s="13" t="str">
+      <c r="J190" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="191" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J191" s="13" t="str">
+      <c r="J191" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="192" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J192" s="13" t="str">
+      <c r="J192" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="193" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J193" s="13" t="str">
+      <c r="J193" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="194" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J194" s="13" t="str">
+      <c r="J194" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="195" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J195" s="13" t="str">
+      <c r="J195" s="12" t="str">
         <f t="shared" ref="J195:J258" si="3">IF(K195="","",IF(K195="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="196" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J196" s="13" t="str">
+      <c r="J196" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="197" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J197" s="13" t="str">
+      <c r="J197" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="198" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J198" s="13" t="str">
+      <c r="J198" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="199" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J199" s="13" t="str">
+      <c r="J199" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="200" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J200" s="13" t="str">
+      <c r="J200" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="201" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J201" s="13" t="str">
+      <c r="J201" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="202" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J202" s="13" t="str">
+      <c r="J202" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="203" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J203" s="13" t="str">
+      <c r="J203" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="204" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J204" s="13" t="str">
+      <c r="J204" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="205" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J205" s="13" t="str">
+      <c r="J205" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="206" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J206" s="13" t="str">
+      <c r="J206" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="207" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J207" s="13" t="str">
+      <c r="J207" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="208" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J208" s="13" t="str">
+      <c r="J208" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="209" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J209" s="13" t="str">
+      <c r="J209" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="210" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J210" s="13" t="str">
+      <c r="J210" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="211" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J211" s="13" t="str">
+      <c r="J211" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="212" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J212" s="13" t="str">
+      <c r="J212" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="213" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J213" s="13" t="str">
+      <c r="J213" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="214" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J214" s="13" t="str">
+      <c r="J214" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="215" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J215" s="13" t="str">
+      <c r="J215" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="216" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J216" s="13" t="str">
+      <c r="J216" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="217" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J217" s="13" t="str">
+      <c r="J217" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="218" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J218" s="13" t="str">
+      <c r="J218" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="219" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J219" s="13" t="str">
+      <c r="J219" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="220" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J220" s="13" t="str">
+      <c r="J220" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="221" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J221" s="13" t="str">
+      <c r="J221" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="222" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J222" s="13" t="str">
+      <c r="J222" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="223" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J223" s="13" t="str">
+      <c r="J223" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="224" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J224" s="13" t="str">
+      <c r="J224" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="225" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J225" s="13" t="str">
+      <c r="J225" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="226" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J226" s="13" t="str">
+      <c r="J226" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="227" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J227" s="13" t="str">
+      <c r="J227" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="228" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J228" s="13" t="str">
+      <c r="J228" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="229" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J229" s="13" t="str">
+      <c r="J229" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="230" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J230" s="13" t="str">
+      <c r="J230" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="231" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J231" s="13" t="str">
+      <c r="J231" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="232" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J232" s="13" t="str">
+      <c r="J232" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="233" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J233" s="13" t="str">
+      <c r="J233" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="234" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J234" s="13" t="str">
+      <c r="J234" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="235" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J235" s="13" t="str">
+      <c r="J235" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="236" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J236" s="13" t="str">
+      <c r="J236" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="237" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J237" s="13" t="str">
+      <c r="J237" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="238" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J238" s="13" t="str">
+      <c r="J238" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="239" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J239" s="13" t="str">
+      <c r="J239" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="240" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J240" s="13" t="str">
+      <c r="J240" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="241" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J241" s="13" t="str">
+      <c r="J241" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="242" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J242" s="13" t="str">
+      <c r="J242" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="243" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J243" s="13" t="str">
+      <c r="J243" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="244" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J244" s="13" t="str">
+      <c r="J244" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="245" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J245" s="13" t="str">
+      <c r="J245" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="246" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J246" s="13" t="str">
+      <c r="J246" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="247" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J247" s="13" t="str">
+      <c r="J247" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="248" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J248" s="13" t="str">
+      <c r="J248" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="249" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J249" s="13" t="str">
+      <c r="J249" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="250" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J250" s="13" t="str">
+      <c r="J250" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="251" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J251" s="13" t="str">
+      <c r="J251" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="252" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J252" s="13" t="str">
+      <c r="J252" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="253" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J253" s="13" t="str">
+      <c r="J253" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="254" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J254" s="13" t="str">
+      <c r="J254" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="255" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J255" s="13" t="str">
+      <c r="J255" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="256" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J256" s="13" t="str">
+      <c r="J256" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="257" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J257" s="13" t="str">
+      <c r="J257" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="258" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J258" s="13" t="str">
+      <c r="J258" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="259" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J259" s="13" t="str">
+      <c r="J259" s="12" t="str">
         <f t="shared" ref="J259:J322" si="4">IF(K259="","",IF(K259="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="260" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J260" s="13" t="str">
+      <c r="J260" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="261" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J261" s="13" t="str">
+      <c r="J261" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="262" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J262" s="13" t="str">
+      <c r="J262" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="263" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J263" s="13" t="str">
+      <c r="J263" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="264" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J264" s="13" t="str">
+      <c r="J264" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="265" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J265" s="13" t="str">
+      <c r="J265" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="266" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J266" s="13" t="str">
+      <c r="J266" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J267" s="13" t="str">
+      <c r="J267" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="268" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J268" s="13" t="str">
+      <c r="J268" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="269" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J269" s="13" t="str">
+      <c r="J269" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="270" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J270" s="13" t="str">
+      <c r="J270" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J271" s="13" t="str">
+      <c r="J271" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J272" s="13" t="str">
+      <c r="J272" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J273" s="13" t="str">
+      <c r="J273" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J274" s="13" t="str">
+      <c r="J274" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J275" s="13" t="str">
+      <c r="J275" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J276" s="13" t="str">
+      <c r="J276" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J277" s="13" t="str">
+      <c r="J277" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J278" s="13" t="str">
+      <c r="J278" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J279" s="13" t="str">
+      <c r="J279" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J280" s="13" t="str">
+      <c r="J280" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J281" s="13" t="str">
+      <c r="J281" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J282" s="13" t="str">
+      <c r="J282" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="283" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J283" s="13" t="str">
+      <c r="J283" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="284" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J284" s="13" t="str">
+      <c r="J284" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="285" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J285" s="13" t="str">
+      <c r="J285" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="286" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J286" s="13" t="str">
+      <c r="J286" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="287" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J287" s="13" t="str">
+      <c r="J287" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="288" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J288" s="13" t="str">
+      <c r="J288" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="289" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J289" s="13" t="str">
+      <c r="J289" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="290" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J290" s="13" t="str">
+      <c r="J290" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="291" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J291" s="13" t="str">
+      <c r="J291" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="292" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J292" s="13" t="str">
+      <c r="J292" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="293" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J293" s="13" t="str">
+      <c r="J293" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="294" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J294" s="13" t="str">
+      <c r="J294" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="295" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J295" s="13" t="str">
+      <c r="J295" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J296" s="13" t="str">
+      <c r="J296" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J297" s="13" t="str">
+      <c r="J297" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J298" s="13" t="str">
+      <c r="J298" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J299" s="13" t="str">
+      <c r="J299" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J300" s="13" t="str">
+      <c r="J300" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J301" s="13" t="str">
+      <c r="J301" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J302" s="13" t="str">
+      <c r="J302" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J303" s="13" t="str">
+      <c r="J303" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J304" s="13" t="str">
+      <c r="J304" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J305" s="13" t="str">
+      <c r="J305" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J306" s="13" t="str">
+      <c r="J306" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J307" s="13" t="str">
+      <c r="J307" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J308" s="13" t="str">
+      <c r="J308" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J309" s="13" t="str">
+      <c r="J309" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J310" s="13" t="str">
+      <c r="J310" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J311" s="13" t="str">
+      <c r="J311" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J312" s="13" t="str">
+      <c r="J312" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J313" s="13" t="str">
+      <c r="J313" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J314" s="13" t="str">
+      <c r="J314" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J315" s="13" t="str">
+      <c r="J315" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J316" s="13" t="str">
+      <c r="J316" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J317" s="13" t="str">
+      <c r="J317" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J318" s="13" t="str">
+      <c r="J318" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J319" s="13" t="str">
+      <c r="J319" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J320" s="13" t="str">
+      <c r="J320" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J321" s="13" t="str">
+      <c r="J321" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J322" s="13" t="str">
+      <c r="J322" s="12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J323" s="13" t="str">
+      <c r="J323" s="12" t="str">
         <f t="shared" ref="J323:J386" si="5">IF(K323="","",IF(K323="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="324" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J324" s="13" t="str">
+      <c r="J324" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J325" s="13" t="str">
+      <c r="J325" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J326" s="13" t="str">
+      <c r="J326" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J327" s="13" t="str">
+      <c r="J327" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J328" s="13" t="str">
+      <c r="J328" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J329" s="13" t="str">
+      <c r="J329" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J330" s="13" t="str">
+      <c r="J330" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J331" s="13" t="str">
+      <c r="J331" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J332" s="13" t="str">
+      <c r="J332" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J333" s="13" t="str">
+      <c r="J333" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J334" s="13" t="str">
+      <c r="J334" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J335" s="13" t="str">
+      <c r="J335" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J336" s="13" t="str">
+      <c r="J336" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J337" s="13" t="str">
+      <c r="J337" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J338" s="13" t="str">
+      <c r="J338" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J339" s="13" t="str">
+      <c r="J339" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J340" s="13" t="str">
+      <c r="J340" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J341" s="13" t="str">
+      <c r="J341" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J342" s="13" t="str">
+      <c r="J342" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J343" s="13" t="str">
+      <c r="J343" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J344" s="13" t="str">
+      <c r="J344" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J345" s="13" t="str">
+      <c r="J345" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J346" s="13" t="str">
+      <c r="J346" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J347" s="13" t="str">
+      <c r="J347" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J348" s="13" t="str">
+      <c r="J348" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J349" s="13" t="str">
+      <c r="J349" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J350" s="13" t="str">
+      <c r="J350" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J351" s="13" t="str">
+      <c r="J351" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J352" s="13" t="str">
+      <c r="J352" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J353" s="13" t="str">
+      <c r="J353" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="354" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J354" s="13" t="str">
+      <c r="J354" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J355" s="13" t="str">
+      <c r="J355" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J356" s="13" t="str">
+      <c r="J356" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J357" s="13" t="str">
+      <c r="J357" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J358" s="13" t="str">
+      <c r="J358" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J359" s="13" t="str">
+      <c r="J359" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J360" s="13" t="str">
+      <c r="J360" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J361" s="13" t="str">
+      <c r="J361" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J362" s="13" t="str">
+      <c r="J362" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J363" s="13" t="str">
+      <c r="J363" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J364" s="13" t="str">
+      <c r="J364" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J365" s="13" t="str">
+      <c r="J365" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J366" s="13" t="str">
+      <c r="J366" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J367" s="13" t="str">
+      <c r="J367" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J368" s="13" t="str">
+      <c r="J368" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J369" s="13" t="str">
+      <c r="J369" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J370" s="13" t="str">
+      <c r="J370" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J371" s="13" t="str">
+      <c r="J371" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J372" s="13" t="str">
+      <c r="J372" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J373" s="13" t="str">
+      <c r="J373" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J374" s="13" t="str">
+      <c r="J374" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J375" s="13" t="str">
+      <c r="J375" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J376" s="13" t="str">
+      <c r="J376" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J377" s="13" t="str">
+      <c r="J377" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J378" s="13" t="str">
+      <c r="J378" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J379" s="13" t="str">
+      <c r="J379" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J380" s="13" t="str">
+      <c r="J380" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J381" s="13" t="str">
+      <c r="J381" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J382" s="13" t="str">
+      <c r="J382" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J383" s="13" t="str">
+      <c r="J383" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J384" s="13" t="str">
+      <c r="J384" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J385" s="13" t="str">
+      <c r="J385" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J386" s="13" t="str">
+      <c r="J386" s="12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J387" s="13" t="str">
+      <c r="J387" s="12" t="str">
         <f t="shared" ref="J387:J450" si="6">IF(K387="","",IF(K387="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="388" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J388" s="13" t="str">
+      <c r="J388" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J389" s="13" t="str">
+      <c r="J389" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J390" s="13" t="str">
+      <c r="J390" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J391" s="13" t="str">
+      <c r="J391" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J392" s="13" t="str">
+      <c r="J392" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J393" s="13" t="str">
+      <c r="J393" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J394" s="13" t="str">
+      <c r="J394" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J395" s="13" t="str">
+      <c r="J395" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J396" s="13" t="str">
+      <c r="J396" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J397" s="13" t="str">
+      <c r="J397" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J398" s="13" t="str">
+      <c r="J398" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J399" s="13" t="str">
+      <c r="J399" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J400" s="13" t="str">
+      <c r="J400" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J401" s="13" t="str">
+      <c r="J401" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J402" s="13" t="str">
+      <c r="J402" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J403" s="13" t="str">
+      <c r="J403" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J404" s="13" t="str">
+      <c r="J404" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J405" s="13" t="str">
+      <c r="J405" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J406" s="13" t="str">
+      <c r="J406" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J407" s="13" t="str">
+      <c r="J407" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J408" s="13" t="str">
+      <c r="J408" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J409" s="13" t="str">
+      <c r="J409" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J410" s="13" t="str">
+      <c r="J410" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J411" s="13" t="str">
+      <c r="J411" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J412" s="13" t="str">
+      <c r="J412" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J413" s="13" t="str">
+      <c r="J413" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J414" s="13" t="str">
+      <c r="J414" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J415" s="13" t="str">
+      <c r="J415" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J416" s="13" t="str">
+      <c r="J416" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J417" s="13" t="str">
+      <c r="J417" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="418" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J418" s="13" t="str">
+      <c r="J418" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J419" s="13" t="str">
+      <c r="J419" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J420" s="13" t="str">
+      <c r="J420" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J421" s="13" t="str">
+      <c r="J421" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J422" s="13" t="str">
+      <c r="J422" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J423" s="13" t="str">
+      <c r="J423" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J424" s="13" t="str">
+      <c r="J424" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J425" s="13" t="str">
+      <c r="J425" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J426" s="13" t="str">
+      <c r="J426" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J427" s="13" t="str">
+      <c r="J427" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J428" s="13" t="str">
+      <c r="J428" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J429" s="13" t="str">
+      <c r="J429" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J430" s="13" t="str">
+      <c r="J430" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J431" s="13" t="str">
+      <c r="J431" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J432" s="13" t="str">
+      <c r="J432" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J433" s="13" t="str">
+      <c r="J433" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J434" s="13" t="str">
+      <c r="J434" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J435" s="13" t="str">
+      <c r="J435" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J436" s="13" t="str">
+      <c r="J436" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J437" s="13" t="str">
+      <c r="J437" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J438" s="13" t="str">
+      <c r="J438" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J439" s="13" t="str">
+      <c r="J439" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J440" s="13" t="str">
+      <c r="J440" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J441" s="13" t="str">
+      <c r="J441" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J442" s="13" t="str">
+      <c r="J442" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J443" s="13" t="str">
+      <c r="J443" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J444" s="13" t="str">
+      <c r="J444" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J445" s="13" t="str">
+      <c r="J445" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J446" s="13" t="str">
+      <c r="J446" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J447" s="13" t="str">
+      <c r="J447" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J448" s="13" t="str">
+      <c r="J448" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J449" s="13" t="str">
+      <c r="J449" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J450" s="13" t="str">
+      <c r="J450" s="12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J451" s="13" t="str">
+      <c r="J451" s="12" t="str">
         <f t="shared" ref="J451:J514" si="7">IF(K451="","",IF(K451="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="452" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J452" s="13" t="str">
+      <c r="J452" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J453" s="13" t="str">
+      <c r="J453" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J454" s="13" t="str">
+      <c r="J454" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J455" s="13" t="str">
+      <c r="J455" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J456" s="13" t="str">
+      <c r="J456" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J457" s="13" t="str">
+      <c r="J457" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J458" s="13" t="str">
+      <c r="J458" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J459" s="13" t="str">
+      <c r="J459" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J460" s="13" t="str">
+      <c r="J460" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J461" s="13" t="str">
+      <c r="J461" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J462" s="13" t="str">
+      <c r="J462" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J463" s="13" t="str">
+      <c r="J463" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J464" s="13" t="str">
+      <c r="J464" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J465" s="13" t="str">
+      <c r="J465" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J466" s="13" t="str">
+      <c r="J466" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J467" s="13" t="str">
+      <c r="J467" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J468" s="13" t="str">
+      <c r="J468" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J469" s="13" t="str">
+      <c r="J469" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J470" s="13" t="str">
+      <c r="J470" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J471" s="13" t="str">
+      <c r="J471" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J472" s="13" t="str">
+      <c r="J472" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J473" s="13" t="str">
+      <c r="J473" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J474" s="13" t="str">
+      <c r="J474" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J475" s="13" t="str">
+      <c r="J475" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J476" s="13" t="str">
+      <c r="J476" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J477" s="13" t="str">
+      <c r="J477" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J478" s="13" t="str">
+      <c r="J478" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J479" s="13" t="str">
+      <c r="J479" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J480" s="13" t="str">
+      <c r="J480" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J481" s="13" t="str">
+      <c r="J481" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="482" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J482" s="13" t="str">
+      <c r="J482" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J483" s="13" t="str">
+      <c r="J483" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J484" s="13" t="str">
+      <c r="J484" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J485" s="13" t="str">
+      <c r="J485" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J486" s="13" t="str">
+      <c r="J486" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J487" s="13" t="str">
+      <c r="J487" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J488" s="13" t="str">
+      <c r="J488" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J489" s="13" t="str">
+      <c r="J489" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J490" s="13" t="str">
+      <c r="J490" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J491" s="13" t="str">
+      <c r="J491" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J492" s="13" t="str">
+      <c r="J492" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J493" s="13" t="str">
+      <c r="J493" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J494" s="13" t="str">
+      <c r="J494" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J495" s="13" t="str">
+      <c r="J495" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J496" s="13" t="str">
+      <c r="J496" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J497" s="13" t="str">
+      <c r="J497" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J498" s="13" t="str">
+      <c r="J498" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J499" s="13" t="str">
+      <c r="J499" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J500" s="13" t="str">
+      <c r="J500" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J501" s="13" t="str">
+      <c r="J501" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J502" s="13" t="str">
+      <c r="J502" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J503" s="13" t="str">
+      <c r="J503" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J504" s="13" t="str">
+      <c r="J504" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J505" s="13" t="str">
+      <c r="J505" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J506" s="13" t="str">
+      <c r="J506" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J507" s="13" t="str">
+      <c r="J507" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J508" s="13" t="str">
+      <c r="J508" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J509" s="13" t="str">
+      <c r="J509" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J510" s="13" t="str">
+      <c r="J510" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J511" s="13" t="str">
+      <c r="J511" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J512" s="13" t="str">
+      <c r="J512" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J513" s="13" t="str">
+      <c r="J513" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J514" s="13" t="str">
+      <c r="J514" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J515" s="13" t="str">
+      <c r="J515" s="12" t="str">
         <f t="shared" ref="J515:J578" si="8">IF(K515="","",IF(K515="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="516" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J516" s="13" t="str">
+      <c r="J516" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J517" s="13" t="str">
+      <c r="J517" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J518" s="13" t="str">
+      <c r="J518" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J519" s="13" t="str">
+      <c r="J519" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J520" s="13" t="str">
+      <c r="J520" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J521" s="13" t="str">
+      <c r="J521" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J522" s="13" t="str">
+      <c r="J522" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J523" s="13" t="str">
+      <c r="J523" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J524" s="13" t="str">
+      <c r="J524" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J525" s="13" t="str">
+      <c r="J525" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J526" s="13" t="str">
+      <c r="J526" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J527" s="13" t="str">
+      <c r="J527" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J528" s="13" t="str">
+      <c r="J528" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J529" s="13" t="str">
+      <c r="J529" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J530" s="13" t="str">
+      <c r="J530" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J531" s="13" t="str">
+      <c r="J531" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J532" s="13" t="str">
+      <c r="J532" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J533" s="13" t="str">
+      <c r="J533" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J534" s="13" t="str">
+      <c r="J534" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J535" s="13" t="str">
+      <c r="J535" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J536" s="13" t="str">
+      <c r="J536" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J537" s="13" t="str">
+      <c r="J537" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J538" s="13" t="str">
+      <c r="J538" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J539" s="13" t="str">
+      <c r="J539" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J540" s="13" t="str">
+      <c r="J540" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J541" s="13" t="str">
+      <c r="J541" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J542" s="13" t="str">
+      <c r="J542" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J543" s="13" t="str">
+      <c r="J543" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J544" s="13" t="str">
+      <c r="J544" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J545" s="13" t="str">
+      <c r="J545" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="546" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J546" s="13" t="str">
+      <c r="J546" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J547" s="13" t="str">
+      <c r="J547" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J548" s="13" t="str">
+      <c r="J548" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J549" s="13" t="str">
+      <c r="J549" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J550" s="13" t="str">
+      <c r="J550" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J551" s="13" t="str">
+      <c r="J551" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J552" s="13" t="str">
+      <c r="J552" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J553" s="13" t="str">
+      <c r="J553" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J554" s="13" t="str">
+      <c r="J554" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J555" s="13" t="str">
+      <c r="J555" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J556" s="13" t="str">
+      <c r="J556" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J557" s="13" t="str">
+      <c r="J557" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J558" s="13" t="str">
+      <c r="J558" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J559" s="13" t="str">
+      <c r="J559" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J560" s="13" t="str">
+      <c r="J560" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J561" s="13" t="str">
+      <c r="J561" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J562" s="13" t="str">
+      <c r="J562" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J563" s="13" t="str">
+      <c r="J563" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J564" s="13" t="str">
+      <c r="J564" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J565" s="13" t="str">
+      <c r="J565" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J566" s="13" t="str">
+      <c r="J566" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J567" s="13" t="str">
+      <c r="J567" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J568" s="13" t="str">
+      <c r="J568" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J569" s="13" t="str">
+      <c r="J569" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J570" s="13" t="str">
+      <c r="J570" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J571" s="13" t="str">
+      <c r="J571" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J572" s="13" t="str">
+      <c r="J572" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J573" s="13" t="str">
+      <c r="J573" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J574" s="13" t="str">
+      <c r="J574" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J575" s="13" t="str">
+      <c r="J575" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J576" s="13" t="str">
+      <c r="J576" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J577" s="13" t="str">
+      <c r="J577" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J578" s="13" t="str">
+      <c r="J578" s="12" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J579" s="13" t="str">
+      <c r="J579" s="12" t="str">
         <f t="shared" ref="J579:J642" si="9">IF(K579="","",IF(K579="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="580" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J580" s="13" t="str">
+      <c r="J580" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J581" s="13" t="str">
+      <c r="J581" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J582" s="13" t="str">
+      <c r="J582" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J583" s="13" t="str">
+      <c r="J583" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J584" s="13" t="str">
+      <c r="J584" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J585" s="13" t="str">
+      <c r="J585" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J586" s="13" t="str">
+      <c r="J586" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J587" s="13" t="str">
+      <c r="J587" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J588" s="13" t="str">
+      <c r="J588" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J589" s="13" t="str">
+      <c r="J589" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J590" s="13" t="str">
+      <c r="J590" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J591" s="13" t="str">
+      <c r="J591" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J592" s="13" t="str">
+      <c r="J592" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J593" s="13" t="str">
+      <c r="J593" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J594" s="13" t="str">
+      <c r="J594" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J595" s="13" t="str">
+      <c r="J595" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J596" s="13" t="str">
+      <c r="J596" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J597" s="13" t="str">
+      <c r="J597" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J598" s="13" t="str">
+      <c r="J598" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J599" s="13" t="str">
+      <c r="J599" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J600" s="13" t="str">
+      <c r="J600" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J601" s="13" t="str">
+      <c r="J601" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J602" s="13" t="str">
+      <c r="J602" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J603" s="13" t="str">
+      <c r="J603" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J604" s="13" t="str">
+      <c r="J604" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J605" s="13" t="str">
+      <c r="J605" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J606" s="13" t="str">
+      <c r="J606" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J607" s="13" t="str">
+      <c r="J607" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J608" s="13" t="str">
+      <c r="J608" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J609" s="13" t="str">
+      <c r="J609" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="610" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J610" s="13" t="str">
+      <c r="J610" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J611" s="13" t="str">
+      <c r="J611" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J612" s="13" t="str">
+      <c r="J612" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J613" s="13" t="str">
+      <c r="J613" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J614" s="13" t="str">
+      <c r="J614" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J615" s="13" t="str">
+      <c r="J615" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J616" s="13" t="str">
+      <c r="J616" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J617" s="13" t="str">
+      <c r="J617" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J618" s="13" t="str">
+      <c r="J618" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J619" s="13" t="str">
+      <c r="J619" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J620" s="13" t="str">
+      <c r="J620" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J621" s="13" t="str">
+      <c r="J621" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J622" s="13" t="str">
+      <c r="J622" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J623" s="13" t="str">
+      <c r="J623" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J624" s="13" t="str">
+      <c r="J624" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J625" s="13" t="str">
+      <c r="J625" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J626" s="13" t="str">
+      <c r="J626" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J627" s="13" t="str">
+      <c r="J627" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J628" s="13" t="str">
+      <c r="J628" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J629" s="13" t="str">
+      <c r="J629" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J630" s="13" t="str">
+      <c r="J630" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J631" s="13" t="str">
+      <c r="J631" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J632" s="13" t="str">
+      <c r="J632" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J633" s="13" t="str">
+      <c r="J633" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J634" s="13" t="str">
+      <c r="J634" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J635" s="13" t="str">
+      <c r="J635" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J636" s="13" t="str">
+      <c r="J636" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J637" s="13" t="str">
+      <c r="J637" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J638" s="13" t="str">
+      <c r="J638" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J639" s="13" t="str">
+      <c r="J639" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J640" s="13" t="str">
+      <c r="J640" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J641" s="13" t="str">
+      <c r="J641" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J642" s="13" t="str">
+      <c r="J642" s="12" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J643" s="13" t="str">
+      <c r="J643" s="12" t="str">
         <f t="shared" ref="J643:J673" si="10">IF(K643="","",IF(K643="✖","✖","✔"))</f>
         <v/>
       </c>
     </row>
     <row r="644" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J644" s="13" t="str">
+      <c r="J644" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J645" s="13" t="str">
+      <c r="J645" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J646" s="13" t="str">
+      <c r="J646" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J647" s="13" t="str">
+      <c r="J647" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J648" s="13" t="str">
+      <c r="J648" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J649" s="13" t="str">
+      <c r="J649" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J650" s="13" t="str">
+      <c r="J650" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J651" s="13" t="str">
+      <c r="J651" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J652" s="13" t="str">
+      <c r="J652" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J653" s="13" t="str">
+      <c r="J653" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J654" s="13" t="str">
+      <c r="J654" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J655" s="13" t="str">
+      <c r="J655" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J656" s="13" t="str">
+      <c r="J656" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J657" s="13" t="str">
+      <c r="J657" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J658" s="13" t="str">
+      <c r="J658" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J659" s="13" t="str">
+      <c r="J659" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J660" s="13" t="str">
+      <c r="J660" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J661" s="13" t="str">
+      <c r="J661" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J662" s="13" t="str">
+      <c r="J662" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J663" s="13" t="str">
+      <c r="J663" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J664" s="13" t="str">
+      <c r="J664" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J665" s="13" t="str">
+      <c r="J665" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J666" s="13" t="str">
+      <c r="J666" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J667" s="13" t="str">
+      <c r="J667" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J668" s="13" t="str">
+      <c r="J668" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J669" s="13" t="str">
+      <c r="J669" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J670" s="13" t="str">
+      <c r="J670" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J671" s="13" t="str">
+      <c r="J671" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J672" s="13" t="str">
+      <c r="J672" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J673" s="13" t="str">
+      <c r="J673" s="12" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -5332,7 +5335,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -5340,7 +5343,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -5348,7 +5351,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5356,27 +5359,27 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>46</v>
       </c>
     </row>

--- a/Template.xlsx
+++ b/Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Nextcloud\Spyro\Documents\Projects\Software\Cardmarket-Price-Updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42CBE37-F2A5-4483-8E3F-CDDE8200FB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49874134-8653-471C-B5C6-34D34740C922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>Release Date</t>
   </si>
@@ -94,7 +96,7 @@
     <t>NKC1-EN002</t>
   </si>
   <si>
-    <t>2026-03-20</t>
+    <t>2026-04-11</t>
   </si>
   <si>
     <t>Prismatic Secret Rare</t>
@@ -261,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -307,6 +309,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -836,11 +841,11 @@
       <c r="E2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="10">
-        <v>237.33</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>19</v>
+      <c r="F2" s="17">
+        <v>243.21</v>
+      </c>
+      <c r="G2" s="11">
+        <v>46123</v>
       </c>
       <c r="H2" s="9">
         <v>845882</v>
@@ -860,7 +865,7 @@
       </c>
       <c r="M2" s="2">
         <f>SUMIFS(F:F, J:J, "&lt;&gt;✖", J:J, "&lt;&gt;")</f>
-        <v>28082.23</v>
+        <v>28799.95</v>
       </c>
       <c r="N2" s="6">
         <f>COUNTIF(K:K,"✖")</f>
@@ -887,8 +892,8 @@
       <c r="E3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="10">
-        <v>158.11000000000001</v>
+      <c r="F3" s="17">
+        <v>116.06</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>19</v>
@@ -925,8 +930,8 @@
       <c r="D4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="10">
-        <v>26328.87</v>
+      <c r="F4" s="17">
+        <v>26980.9</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>19</v>
@@ -970,8 +975,8 @@
       <c r="E5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="10">
-        <v>1248.46</v>
+      <c r="F5" s="17">
+        <v>1351.48</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>19</v>
@@ -1014,8 +1019,8 @@
       <c r="E6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="10">
-        <v>267.57</v>
+      <c r="F6" s="17">
+        <v>224.36</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>19</v>
@@ -1035,7 +1040,7 @@
       </c>
       <c r="M6" s="3">
         <f>SUM(F:F)-M2</f>
-        <v>158.10999999999694</v>
+        <v>116.06000000000131</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>

--- a/Template.xlsx
+++ b/Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Nextcloud\Spyro\Documents\Projects\Software\Cardmarket-Price-Updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49874134-8653-471C-B5C6-34D34740C922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8F5771-7B0B-4F86-9A95-A679B99B4A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cardmarket Price Updater" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>Release Date</t>
   </si>
@@ -78,7 +78,7 @@
     <t>Collection Value (£)</t>
   </si>
   <si>
-    <t>Remaing Cards</t>
+    <t>Remaning Cards</t>
   </si>
   <si>
     <t>Total Cards</t>
@@ -96,7 +96,7 @@
     <t>NKC1-EN002</t>
   </si>
   <si>
-    <t>2026-04-11</t>
+    <t>2026-04-12</t>
   </si>
   <si>
     <t>Prismatic Secret Rare</t>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>PSA8</t>
+  </si>
+  <si>
+    <t>Ghost Rare</t>
   </si>
 </sst>
 </file>
@@ -774,7 +777,7 @@
     <col min="10" max="11" width="10.28515625" style="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -844,8 +847,8 @@
       <c r="F2" s="17">
         <v>243.21</v>
       </c>
-      <c r="G2" s="11">
-        <v>46123</v>
+      <c r="G2" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="H2" s="9">
         <v>845882</v>
@@ -1027,6 +1030,9 @@
       </c>
       <c r="H6" s="9">
         <v>108490</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="J6" s="12" t="str">
         <f t="shared" si="0"/>

--- a/Template.xlsx
+++ b/Template.xlsx
@@ -96,7 +96,7 @@
     <t>NKC1-EN002</t>
   </si>
   <si>
-    <t>2026-05-21</t>
+    <t>2026-06-27</t>
   </si>
   <si>
     <t>Prismatic Secret Rare</t>
@@ -1130,7 +1130,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="17">
-        <v>372.45</v>
+        <v>376.62</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>19</v>
@@ -1181,7 +1181,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="17">
-        <v>55.1</v>
+        <v>131.9</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>19</v>
@@ -1219,7 +1219,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="17">
-        <v>7962.67</v>
+        <v>7934.89</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>19</v>
@@ -1264,7 +1264,7 @@
         <v>36</v>
       </c>
       <c r="F5" s="17">
-        <v>1570.66</v>
+        <v>1718.97</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>19</v>
@@ -1308,7 +1308,7 @@
         <v>42</v>
       </c>
       <c r="F6" s="17">
-        <v>288.51</v>
+        <v>274.33</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>19</v>
@@ -4881,53 +4881,53 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:E1048576 H1:K1048576">
-    <cfRule type="expression" dxfId="37" priority="4">
+    <cfRule type="expression" dxfId="14" priority="4">
       <formula>$K1="PSA10"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="5">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>OR($K1="PSA8",$K1="PSA9")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="8">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>$K1="Unlimited"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>AND($J1="✔", $K1&lt;&gt;"unlimited")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$J1="✖"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:K1048576">
-    <cfRule type="expression" dxfId="42" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$K1=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F1048576">
-    <cfRule type="aboveAverage" dxfId="43" priority="11" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="44" priority="12"/>
+    <cfRule type="aboveAverage" dxfId="0" priority="11" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="1" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K1048576">
-    <cfRule type="containsText" dxfId="45" priority="21" operator="containsText" text="✖">
+    <cfRule type="containsText" dxfId="6" priority="21" operator="containsText" text="✖">
       <formula>NOT(ISERROR(SEARCH("✖",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="22" operator="containsText" text="Unlimited">
+    <cfRule type="containsText" dxfId="5" priority="22" operator="containsText" text="Unlimited">
       <formula>NOT(ISERROR(SEARCH("Unlimited",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="23" operator="containsText" text="LIMITED">
+    <cfRule type="containsText" dxfId="2" priority="23" operator="containsText" text="LIMITED">
       <formula>NOT(ISERROR(SEARCH("LIMITED",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="24" operator="containsText" text="✔">
+    <cfRule type="containsText" dxfId="2" priority="24" operator="containsText" text="✔">
       <formula>NOT(ISERROR(SEARCH("✔",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="25" operator="containsText" text="1st Edition">
+    <cfRule type="containsText" dxfId="2" priority="25" operator="containsText" text="1st Edition">
       <formula>NOT(ISERROR(SEARCH("1st Edition",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L1048576">
-    <cfRule type="expression" dxfId="44" priority="15">
+    <cfRule type="expression" dxfId="1" priority="15">
       <formula>L2 &gt; F2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="16">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>L2 &lt; F2</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Template.xlsx
+++ b/Template.xlsx
@@ -96,7 +96,7 @@
     <t>NKC1-EN002</t>
   </si>
   <si>
-    <t>2026-06-27</t>
+    <t>2026-08-26</t>
   </si>
   <si>
     <t>Prismatic Secret Rare</t>
@@ -1130,7 +1130,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="17">
-        <v>376.62</v>
+        <v>402.53</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>19</v>
@@ -1181,7 +1181,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="17">
-        <v>131.9</v>
+        <v>467.11</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>19</v>
@@ -1219,7 +1219,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="17">
-        <v>7934.89</v>
+        <v>9876.27</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>19</v>
@@ -1264,7 +1264,7 @@
         <v>36</v>
       </c>
       <c r="F5" s="17">
-        <v>1718.97</v>
+        <v>2119.74</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>19</v>
@@ -1308,7 +1308,7 @@
         <v>42</v>
       </c>
       <c r="F6" s="17">
-        <v>274.33</v>
+        <v>245.4</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>19</v>
